--- a/Code_Blockchain_Resilience_Risk_Sensing_Decision_Intelligence_2/Risk_Velocity_FINAL_QUALITATIVE_ANALYSIS_20260827_130334.xlsx
+++ b/Code_Blockchain_Resilience_Risk_Sensing_Decision_Intelligence_2/Risk_Velocity_FINAL_QUALITATIVE_ANALYSIS_20260827_130334.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="11_BFAC153038F8A64DC49161AAEA7E660A8F8D4B87" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AB82958-54D2-4A25-8085-1E5F83DD9F54}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Original_RV_Evidence" sheetId="1" r:id="rId1"/>
